--- a/data/trans_dic/IP2002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les han extraído dientes por caries o por otro motivo</t>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 14,4</t>
+          <t>5,06; 14,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,64</t>
+          <t>0,75; 6,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,52</t>
+          <t>2,29; 11,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 14,34</t>
+          <t>4,98; 13,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 12,22</t>
+          <t>3,08; 12,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,38</t>
+          <t>2,2; 9,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,13</t>
+          <t>0,79; 7,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,02</t>
+          <t>3,21; 11,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,24</t>
+          <t>4,86; 11,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,54</t>
+          <t>1,92; 6,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,36</t>
+          <t>1,96; 7,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,3</t>
+          <t>5,0; 10,93</t>
         </is>
       </c>
     </row>
@@ -856,47 +857,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,1</t>
+          <t>2,66; 13,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,15</t>
+          <t>0,83; 8,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,63</t>
+          <t>0,72; 6,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,91</t>
+          <t>2,45; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,91</t>
+          <t>1,59; 9,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,11</t>
+          <t>1,37; 8,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,47</t>
+          <t>1,24; 7,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,14</t>
+          <t>1,22; 8,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,48</t>
+          <t>2,9; 8,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,47</t>
+          <t>1,61; 5,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,87</t>
+          <t>2,39; 8,28</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 13,34</t>
+          <t>2,32; 12,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,55</t>
+          <t>0,8; 7,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 13,33</t>
+          <t>2,57; 14,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 16,44</t>
+          <t>2,98; 16,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,67</t>
+          <t>2,76; 10,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,58</t>
+          <t>1,51; 9,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 12,46</t>
+          <t>2,83; 13,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,46</t>
+          <t>1,23; 11,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,5</t>
+          <t>3,38; 9,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,65</t>
+          <t>1,57; 6,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,82</t>
+          <t>3,79; 11,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,41</t>
+          <t>2,55; 10,21</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,63</t>
+          <t>3,25; 8,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,97</t>
+          <t>4,11; 10,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,55</t>
+          <t>3,43; 8,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,42</t>
+          <t>3,19; 8,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,08</t>
+          <t>3,97; 9,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,74</t>
+          <t>4,12; 9,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,62</t>
+          <t>4,23; 10,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,86</t>
+          <t>2,45; 7,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,4</t>
+          <t>4,24; 8,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,6</t>
+          <t>4,45; 8,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,38</t>
+          <t>4,55; 8,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,23</t>
+          <t>3,33; 7,15</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,37</t>
+          <t>3,9; 12,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,9</t>
+          <t>6,26; 14,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 13,68</t>
+          <t>5,06; 13,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,38</t>
+          <t>2,39; 10,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,77</t>
+          <t>6,88; 15,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 17,31</t>
+          <t>7,59; 17,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,78</t>
+          <t>1,39; 7,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,51</t>
+          <t>0,95; 7,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 12,52</t>
+          <t>6,55; 12,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 14,28</t>
+          <t>7,69; 14,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,12</t>
+          <t>4,23; 9,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,8</t>
+          <t>2,09; 6,85</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,5</t>
+          <t>2,71; 12,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,38</t>
+          <t>0,0; 9,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,53</t>
+          <t>2,89; 15,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,44</t>
+          <t>0,0; 13,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,04</t>
+          <t>2,98; 13,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,38; 15,23</t>
+          <t>3,41; 14,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,01</t>
+          <t>1,03; 9,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,91</t>
+          <t>1,33; 13,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,58</t>
+          <t>3,84; 10,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,81</t>
+          <t>2,9; 10,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,8</t>
+          <t>2,9; 9,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,73</t>
+          <t>1,77; 10,49</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,48</t>
+          <t>5,12; 8,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,1</t>
+          <t>4,12; 7,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,79</t>
+          <t>4,57; 8,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,79</t>
+          <t>4,43; 7,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,58</t>
+          <t>5,33; 8,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,37</t>
+          <t>5,11; 8,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,45</t>
+          <t>3,7; 6,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,27</t>
+          <t>3,23; 6,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 7,96</t>
+          <t>5,61; 7,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,27</t>
+          <t>5,09; 7,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,6</t>
+          <t>4,56; 6,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,5</t>
+          <t>4,19; 6,37</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9040</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5783</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3787</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8836</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14323</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5846</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7062</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>17876</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4881; 14223</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>628; 5699</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1770; 9086</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5144; 14416</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2803; 11105</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1820; 7521</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>708; 6319</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4367; 15269</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9097; 21143</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3197; 10941</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3277; 12305</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>11974; 26163</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5177</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8407</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6226</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6233</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8710</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2173; 10603</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>720; 7102</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>703; 6464</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2322; 10758</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1324; 8072</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1260; 7390</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1313; 7664</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1135; 8029</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4771; 14763</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2800; 11372</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3259; 11253</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4501; 15556</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4242</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4086</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3765</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5571</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4701</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9814</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1502; 8183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>652; 5962</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1502; 8213</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1486; 8421</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2700; 10299</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1234; 7399</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2006; 9238</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>778; 7161</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5493; 15603</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2560; 10106</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4904; 14551</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2884; 11541</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>10476</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12154</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11674</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12042</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13627</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13843</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>22518</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25781</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25696</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>21595</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6233; 16105</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7815; 19160</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7117; 17955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6824; 18883</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7514; 17741</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8678; 20539</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8592; 21007</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5212; 15923</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>16126; 30731</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>17842; 34017</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>18699; 34474</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>14203; 30517</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7247</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14090</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11639</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6250</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13160</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15177</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4454</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>20407</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>29268</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>16755</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>10704</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3909; 12693</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8634; 20553</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6621; 18055</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2809; 12094</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8366; 19327</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9982; 22629</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1873; 10444</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1519; 11454</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>14521; 28020</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20708; 38402</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11264; 24622</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5781; 18979</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5297</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3808</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>6624</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1936; 8725</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4742</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1640; 8966</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 9622</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1961; 8622</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2339; 10049</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>673; 5941</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>937; 9529</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5265; 14625</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3443; 12570</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3527; 11962</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2468; 14614</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>40052</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>34481</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>38891</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>38304</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>44529</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>44574</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>32226</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>33528</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>84581</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>79056</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>71833</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>31021; 50925</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25959; 45466</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>28710; 50638</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>28686; 50407</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>34575; 56981</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>34071; 56927</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>24778; 43470</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>23734; 45517</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>70363; 99222</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>65988; 94385</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>59143; 87225</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>57923; 88094</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 14,76</t>
+          <t>4,92; 14,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,79</t>
+          <t>0,76; 6,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 11,76</t>
+          <t>2,18; 11,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 13,96</t>
+          <t>4,93; 13,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 12,21</t>
+          <t>3,11; 11,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,1</t>
+          <t>1,54; 9,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,01</t>
+          <t>0,78; 7,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,22</t>
+          <t>3,43; 11,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,28</t>
+          <t>5,05; 11,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,57</t>
+          <t>1,86; 6,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,35</t>
+          <t>2,24; 7,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,93</t>
+          <t>4,77; 11,07</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 13,0</t>
+          <t>2,74; 11,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,19</t>
+          <t>0,81; 7,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,65</t>
+          <t>0,74; 6,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,36</t>
+          <t>2,19; 10,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,7</t>
+          <t>1,57; 8,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,03</t>
+          <t>1,48; 8,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,26</t>
+          <t>1,25; 7,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 8,61</t>
+          <t>1,35; 9,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,96</t>
+          <t>2,61; 8,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,36</t>
+          <t>1,83; 6,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,55</t>
+          <t>1,45; 5,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,28</t>
+          <t>2,51; 8,02</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 12,65</t>
+          <t>2,99; 14,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,34</t>
+          <t>0,81; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 14,04</t>
+          <t>2,38; 13,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 16,87</t>
+          <t>2,87; 17,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,53</t>
+          <t>2,72; 10,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,08</t>
+          <t>1,52; 8,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,05</t>
+          <t>2,91; 13,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,34</t>
+          <t>1,23; 12,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,6</t>
+          <t>3,44; 9,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,21</t>
+          <t>1,58; 6,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 11,25</t>
+          <t>3,73; 10,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,21</t>
+          <t>2,75; 10,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,4</t>
+          <t>3,24; 8,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,07</t>
+          <t>3,77; 9,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,64</t>
+          <t>3,62; 8,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,83</t>
+          <t>2,95; 8,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,39</t>
+          <t>3,84; 10,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,75</t>
+          <t>3,86; 9,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,34</t>
+          <t>4,23; 10,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,49</t>
+          <t>2,65; 7,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,07</t>
+          <t>4,08; 8,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,48</t>
+          <t>4,62; 8,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,39</t>
+          <t>4,34; 8,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,15</t>
+          <t>3,35; 7,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 12,67</t>
+          <t>4,01; 12,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,91</t>
+          <t>6,76; 14,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,79</t>
+          <t>5,45; 14,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 10,31</t>
+          <t>2,1; 10,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 15,89</t>
+          <t>6,75; 16,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,2</t>
+          <t>7,25; 17,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,73</t>
+          <t>1,64; 8,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,18</t>
+          <t>0,87; 7,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,63</t>
+          <t>6,48; 12,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 14,25</t>
+          <t>7,99; 14,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,26</t>
+          <t>4,19; 9,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,85</t>
+          <t>2,14; 6,94</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 12,2</t>
+          <t>2,85; 12,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,5</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 15,82</t>
+          <t>3,4; 15,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,97</t>
+          <t>0,0; 15,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 13,12</t>
+          <t>2,98; 13,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 14,64</t>
+          <t>2,95; 15,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,14</t>
+          <t>1,02; 8,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,53</t>
+          <t>1,28; 13,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,66</t>
+          <t>3,72; 11,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 10,6</t>
+          <t>2,75; 10,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,83</t>
+          <t>2,78; 10,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,49</t>
+          <t>1,63; 10,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,4</t>
+          <t>5,03; 8,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,22</t>
+          <t>4,13; 7,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,06</t>
+          <t>4,82; 8,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,78</t>
+          <t>4,37; 7,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,79</t>
+          <t>5,42; 8,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,53</t>
+          <t>5,19; 8,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,49</t>
+          <t>3,6; 6,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,19</t>
+          <t>3,29; 6,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 7,91</t>
+          <t>5,68; 8,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,28</t>
+          <t>5,05; 7,2</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,72</t>
+          <t>4,43; 6,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,37</t>
+          <t>4,15; 6,4</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4881; 14223</t>
+          <t>4738; 14163</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>628; 5699</t>
+          <t>642; 5404</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1770; 9086</t>
+          <t>1683; 9254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5144; 14416</t>
+          <t>5095; 14404</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2803; 11105</t>
+          <t>2830; 10803</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1820; 7521</t>
+          <t>1269; 7571</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>708; 6319</t>
+          <t>700; 7177</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4367; 15269</t>
+          <t>4672; 15676</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9097; 21143</t>
+          <t>9464; 21050</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3197; 10941</t>
+          <t>3093; 10546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3277; 12305</t>
+          <t>3749; 12963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11974; 26163</t>
+          <t>11427; 26490</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2173; 10603</t>
+          <t>2236; 9425</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>720; 7102</t>
+          <t>700; 6362</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>703; 6464</t>
+          <t>719; 6082</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2322; 10758</t>
+          <t>2072; 10106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1324; 8072</t>
+          <t>1302; 7070</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1260; 7390</t>
+          <t>1364; 7624</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1313; 7664</t>
+          <t>1324; 7885</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1135; 8029</t>
+          <t>1257; 9098</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4771; 14763</t>
+          <t>4300; 13311</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2800; 11372</t>
+          <t>3267; 11467</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3259; 11253</t>
+          <t>2941; 11644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4501; 15556</t>
+          <t>4714; 15080</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1502; 8183</t>
+          <t>1932; 9365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>652; 5962</t>
+          <t>659; 6089</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1502; 8213</t>
+          <t>1394; 8085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1486; 8421</t>
+          <t>1432; 8575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2700; 10299</t>
+          <t>2658; 10352</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1234; 7399</t>
+          <t>1236; 7104</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2006; 9238</t>
+          <t>2057; 9415</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>778; 7161</t>
+          <t>777; 7678</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5493; 15603</t>
+          <t>5587; 15497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2560; 10106</t>
+          <t>2573; 10126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4904; 14551</t>
+          <t>4827; 13954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2884; 11541</t>
+          <t>3104; 12122</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6233; 16105</t>
+          <t>6219; 16218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7815; 19160</t>
+          <t>7171; 18635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7117; 17955</t>
+          <t>7523; 18070</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6824; 18883</t>
+          <t>6322; 18976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7514; 17741</t>
+          <t>7262; 18989</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8678; 20539</t>
+          <t>8121; 20554</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8592; 21007</t>
+          <t>8586; 20629</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5212; 15923</t>
+          <t>5644; 16946</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16126; 30731</t>
+          <t>15539; 30899</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17842; 34017</t>
+          <t>18524; 35271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18699; 34474</t>
+          <t>17846; 34486</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14203; 30517</t>
+          <t>14308; 30632</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3909; 12693</t>
+          <t>4021; 12961</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8634; 20553</t>
+          <t>9317; 20460</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6621; 18055</t>
+          <t>7131; 19015</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2809; 12094</t>
+          <t>2468; 12198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8366; 19327</t>
+          <t>8205; 19563</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9982; 22629</t>
+          <t>9545; 22513</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1873; 10444</t>
+          <t>2212; 10921</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1519; 11454</t>
+          <t>1387; 11553</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14521; 28020</t>
+          <t>14383; 28788</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20708; 38402</t>
+          <t>21517; 38458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11264; 24622</t>
+          <t>11149; 24787</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5781; 18979</t>
+          <t>5935; 19212</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1936; 8725</t>
+          <t>2041; 9108</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4742</t>
+          <t>0; 4109</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1640; 8966</t>
+          <t>1925; 8957</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 9622</t>
+          <t>0; 10643</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1961; 8622</t>
+          <t>1957; 8609</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2339; 10049</t>
+          <t>2028; 10915</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>673; 5941</t>
+          <t>662; 5738</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>937; 9529</t>
+          <t>900; 9402</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5265; 14625</t>
+          <t>5103; 15514</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3443; 12570</t>
+          <t>3261; 12108</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3527; 11962</t>
+          <t>3385; 12425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2468; 14614</t>
+          <t>2267; 13964</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31021; 50925</t>
+          <t>30499; 50358</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25959; 45466</t>
+          <t>26037; 44502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28710; 50638</t>
+          <t>30253; 50816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28686; 50407</t>
+          <t>28305; 49840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34575; 56981</t>
+          <t>35173; 56369</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34071; 56927</t>
+          <t>34603; 56054</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24778; 43470</t>
+          <t>24119; 42752</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>23734; 45517</t>
+          <t>24162; 46399</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70363; 99222</t>
+          <t>71196; 101792</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65988; 94385</t>
+          <t>65488; 93359</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59143; 87225</t>
+          <t>57503; 85703</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>57923; 88094</t>
+          <t>57365; 88555</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 14,69</t>
+          <t>3,11; 12,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,44</t>
+          <t>1,59; 9,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 11,98</t>
+          <t>0,86; 8,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,95</t>
+          <t>3,32; 11,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,87</t>
+          <t>4,92; 14,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,16</t>
+          <t>0,76; 6,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,96</t>
+          <t>2,03; 11,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 11,52</t>
+          <t>5,01; 14,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 11,23</t>
+          <t>5,01; 11,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,33</t>
+          <t>1,85; 6,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,74</t>
+          <t>2,13; 7,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,07</t>
+          <t>5,14; 11,38</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,55</t>
+          <t>1,57; 8,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,33</t>
+          <t>1,39; 8,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,26</t>
+          <t>1,29; 7,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,67</t>
+          <t>1,0; 8,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,5</t>
+          <t>2,54; 11,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,28</t>
+          <t>0,81; 7,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,47</t>
+          <t>0,73; 6,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 9,76</t>
+          <t>2,19; 10,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,08</t>
+          <t>2,91; 8,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,41</t>
+          <t>1,57; 6,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,74</t>
+          <t>1,44; 5,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,02</t>
+          <t>2,38; 7,65</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,99%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 14,48</t>
+          <t>2,79; 10,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,49</t>
+          <t>1,53; 8,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,82</t>
+          <t>2,88; 12,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 17,18</t>
+          <t>1,25; 11,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 10,58</t>
+          <t>2,97; 13,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,71</t>
+          <t>0,81; 7,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 13,3</t>
+          <t>2,62; 13,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,16</t>
+          <t>2,8; 16,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,54</t>
+          <t>3,02; 9,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,22</t>
+          <t>1,61; 6,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,79</t>
+          <t>3,71; 10,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,72</t>
+          <t>2,85; 10,72</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,46</t>
+          <t>3,95; 10,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,79</t>
+          <t>3,94; 9,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,7</t>
+          <t>4,24; 10,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,87</t>
+          <t>2,53; 8,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 10,05</t>
+          <t>3,3; 8,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,76</t>
+          <t>3,82; 9,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,16</t>
+          <t>3,47; 8,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,97</t>
+          <t>4,39; 10,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,12</t>
+          <t>4,33; 8,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,8</t>
+          <t>4,65; 8,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,39</t>
+          <t>4,55; 8,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,18</t>
+          <t>3,83; 8,15</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,23%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,89%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 12,94</t>
+          <t>6,85; 15,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,84</t>
+          <t>7,22; 17,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 14,53</t>
+          <t>1,32; 7,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,4</t>
+          <t>1,16; 7,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 16,09</t>
+          <t>3,57; 12,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 17,11</t>
+          <t>6,59; 14,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,08</t>
+          <t>5,24; 13,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,24</t>
+          <t>2,46; 10,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,98</t>
+          <t>6,24; 12,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 14,27</t>
+          <t>7,93; 14,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,32</t>
+          <t>3,69; 9,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,94</t>
+          <t>2,1; 7,02</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6,34%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7,62%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>5,41%</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,73</t>
+          <t>3,0; 13,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>3,38; 15,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,8</t>
+          <t>1,03; 9,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,45</t>
+          <t>1,4; 12,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 13,1</t>
+          <t>2,64; 11,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 15,9</t>
+          <t>0,0; 9,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,83</t>
+          <t>3,4; 15,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 13,34</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,3</t>
+          <t>3,79; 10,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,21</t>
+          <t>2,6; 9,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,21</t>
+          <t>2,49; 9,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,02</t>
+          <t>1,36; 7,17</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,61%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,47%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,31</t>
+          <t>5,23; 8,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,06</t>
+          <t>5,14; 8,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,09</t>
+          <t>3,45; 6,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,69</t>
+          <t>3,29; 6,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,69</t>
+          <t>5,12; 8,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,4</t>
+          <t>4,17; 7,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,38</t>
+          <t>4,81; 7,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,31</t>
+          <t>4,72; 7,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,11</t>
+          <t>5,68; 7,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 7,2</t>
+          <t>5,11; 7,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,6</t>
+          <t>4,48; 6,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,4</t>
+          <t>4,3; 6,58</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5783</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3787</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7809</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>8540</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2059</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4346</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9040</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5783</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3787</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>16933</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4738; 14163</t>
+          <t>2831; 11114</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>642; 5404</t>
+          <t>1314; 7754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1683; 9254</t>
+          <t>780; 7329</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5095; 14404</t>
+          <t>4048; 14489</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2830; 10803</t>
+          <t>4739; 13883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1269; 7571</t>
+          <t>636; 5577</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>700; 7177</t>
+          <t>1568; 8896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4672; 15676</t>
+          <t>5105; 14940</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9464; 21050</t>
+          <t>9384; 21061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3093; 10546</t>
+          <t>3075; 10889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3749; 12963</t>
+          <t>3570; 12328</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11427; 26490</t>
+          <t>11493; 25470</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2987</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5011</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2813</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2649</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5177</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3413</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3585</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8184</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2236; 9425</t>
+          <t>1309; 7413</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>700; 6362</t>
+          <t>1283; 7465</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>719; 6082</t>
+          <t>1363; 7878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2072; 10106</t>
+          <t>893; 7869</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1302; 7070</t>
+          <t>2069; 9052</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1364; 7624</t>
+          <t>705; 6204</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1324; 7885</t>
+          <t>713; 6446</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1257; 9098</t>
+          <t>2117; 10332</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4300; 13311</t>
+          <t>4800; 13979</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3267; 11467</t>
+          <t>2808; 11380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2941; 11644</t>
+          <t>2921; 11083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4714; 15080</t>
+          <t>4422; 14241</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5571</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4701</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4242</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2038</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4086</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3765</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4701</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6641</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1932; 9365</t>
+          <t>2734; 10442</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>659; 6089</t>
+          <t>1244; 6992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1394; 8085</t>
+          <t>2038; 8824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1432; 8575</t>
+          <t>703; 6744</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2658; 10352</t>
+          <t>1919; 8628</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1236; 7104</t>
+          <t>658; 6131</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2057; 9415</t>
+          <t>1532; 7794</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>777; 7678</t>
+          <t>1445; 8557</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5587; 15497</t>
+          <t>4901; 15444</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2573; 10126</t>
+          <t>2620; 10825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4827; 13954</t>
+          <t>4802; 13991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3104; 12122</t>
+          <t>3075; 11570</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12042</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13627</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13843</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>10476</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>12154</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11853</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11674</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12042</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13627</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13843</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>21355</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6219; 16218</t>
+          <t>7457; 19052</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7171; 18635</t>
+          <t>8300; 20512</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7523; 18070</t>
+          <t>8621; 21567</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6322; 18976</t>
+          <t>4987; 16092</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7262; 18989</t>
+          <t>6331; 16533</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8121; 20554</t>
+          <t>7272; 18975</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8586; 20629</t>
+          <t>7203; 17774</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5644; 16946</t>
+          <t>7711; 18537</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15539; 30899</t>
+          <t>16469; 31978</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18524; 35271</t>
+          <t>18631; 34497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17846; 34486</t>
+          <t>18681; 34428</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14308; 30632</t>
+          <t>14281; 30384</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13160</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15177</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4279</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7247</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14090</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>11639</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13160</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15177</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5116</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>10697</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4021; 12961</t>
+          <t>8333; 19178</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9317; 20460</t>
+          <t>9502; 22772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7131; 19015</t>
+          <t>1782; 10516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2468; 12198</t>
+          <t>1692; 11014</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8205; 19563</t>
+          <t>3572; 12390</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9545; 22513</t>
+          <t>9082; 20544</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2212; 10921</t>
+          <t>6862; 17914</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1387; 11553</t>
+          <t>2873; 12593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14383; 28788</t>
+          <t>13829; 27776</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21517; 38458</t>
+          <t>21375; 38480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11149; 24787</t>
+          <t>9810; 24249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5935; 19212</t>
+          <t>5519; 18438</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4577</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5297</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3484</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>4535</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1327</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4318</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2397</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4577</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5297</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2266</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>906</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>4390</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2041; 9108</t>
+          <t>1972; 8573</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>2320; 10459</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1925; 8957</t>
+          <t>668; 5858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 10643</t>
+          <t>941; 8452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1957; 8609</t>
+          <t>1891; 8225</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2028; 10915</t>
+          <t>0; 4682</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>662; 5738</t>
+          <t>1926; 8800</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>900; 9402</t>
+          <t>0; 3101</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5103; 15514</t>
+          <t>5208; 14522</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3261; 12108</t>
+          <t>3079; 11628</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3385; 12425</t>
+          <t>3025; 11929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2267; 13964</t>
+          <t>1862; 9859</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>44529</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>44574</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>32226</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>30511</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>40052</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>34481</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>38891</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>38304</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>44529</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>44574</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>32226</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71833</t>
+          <t>68198</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30499; 50358</t>
+          <t>33909; 55609</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26037; 44502</t>
+          <t>34315; 55852</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30253; 50816</t>
+          <t>23092; 43226</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28305; 49840</t>
+          <t>22315; 42212</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35173; 56369</t>
+          <t>31028; 51359</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34603; 56054</t>
+          <t>26246; 44725</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24119; 42752</t>
+          <t>30226; 48952</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24162; 46399</t>
+          <t>28920; 48631</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71196; 101792</t>
+          <t>71285; 99902</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65488; 93359</t>
+          <t>66303; 94324</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57503; 85703</t>
+          <t>58141; 85632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>57365; 88555</t>
+          <t>55562; 84900</t>
         </is>
       </c>
     </row>
